--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="323">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -356,7 +356,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -692,6 +692,22 @@
 booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
   </si>
   <si>
+    <t>EpisodeOfCare.extension:managingOrganization</t>
+  </si>
+  <si>
+    <t>managingOrganization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-managing-organization}
+</t>
+  </si>
+  <si>
+    <t>Managing organization for a period</t>
+  </si>
+  <si>
+    <t>An organization that has assumed responsibility for the episode of care during a given period. Replaces the standard EpisodeOfCare.managingOrganization to allow multiple managing organizations over time.</t>
+  </si>
+  <si>
     <t>EpisodeOfCare.modifierExtension</t>
   </si>
   <si>
@@ -825,7 +841,7 @@
     <t>The type of the episode of care.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/episodeofcare-type</t>
+    <t>http://hl7.org/fhir/ValueSet/episodeofcare-type|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -883,7 +899,7 @@
     <t>The type of diagnosis this condition represents.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnosis-role</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnosis-role|4.0.1</t>
   </si>
   <si>
     <t>EpisodeOfCare.diagnosis.rank</t>
@@ -921,7 +937,7 @@
     <t>EpisodeOfCare.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://ehealth.sundhed.dk/fhir/StructureDefinition/ehealth-organization) &lt;&lt;referenced&gt;&gt;
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -952,7 +968,7 @@
     <t>EpisodeOfCare.referralRequest</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -968,7 +984,7 @@
     <t>EpisodeOfCare.careManager</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -998,7 +1014,7 @@
     <t>EpisodeOfCare.account</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Account)
+    <t xml:space="preserve">Reference(Account|4.0.1)
 </t>
   </si>
   <si>
@@ -1306,7 +1322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM57"/>
+  <dimension ref="A1:AM58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.11328125" customWidth="true" bestFit="true"/>
@@ -4993,11 +5009,13 @@
         <v>217</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>129</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D34" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5010,26 +5028,22 @@
         <v>77</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>130</v>
+        <v>219</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5077,7 +5091,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>221</v>
+        <v>135</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5086,7 +5100,7 @@
         <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>136</v>
@@ -5095,7 +5109,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5110,7 +5124,7 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5123,22 +5137,26 @@
         <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L35" t="s" s="2">
+      <c r="M35" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O35" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5186,7 +5204,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5198,24 +5216,24 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>226</v>
+        <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>227</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5223,22 +5241,22 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I36" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>105</v>
+        <v>228</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>229</v>
@@ -5246,9 +5264,7 @@
       <c r="M36" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="N36" t="s" s="2">
-        <v>231</v>
-      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5273,13 +5289,13 @@
         <v>77</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>77</v>
@@ -5297,13 +5313,13 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
@@ -5312,21 +5328,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5334,30 +5350,32 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I37" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>237</v>
+        <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>235</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>236</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5382,13 +5400,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5406,13 +5424,13 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>77</v>
@@ -5421,21 +5439,21 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>77</v>
+        <v>239</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5446,7 +5464,7 @@
         <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5458,13 +5476,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>164</v>
+        <v>243</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>165</v>
+        <v>244</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5515,25 +5533,25 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -5541,21 +5559,21 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>77</v>
@@ -5567,17 +5585,15 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5626,19 +5642,19 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -5652,14 +5668,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5672,26 +5688,24 @@
         <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="O40" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
       </c>
@@ -5739,7 +5753,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5757,7 +5771,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5772,35 +5786,39 @@
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>105</v>
+        <v>130</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
       </c>
@@ -5824,13 +5842,13 @@
         <v>77</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>232</v>
+        <v>77</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>77</v>
@@ -5848,25 +5866,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -5874,10 +5892,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5900,13 +5918,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>249</v>
+        <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>251</v>
+        <v>235</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5933,13 +5951,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>77</v>
+        <v>237</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>77</v>
+        <v>238</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -5957,7 +5975,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>85</v>
@@ -5983,10 +6001,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5994,10 +6012,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6006,20 +6024,18 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N43" t="s" s="2">
         <v>256</v>
       </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6044,13 +6060,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>257</v>
+        <v>77</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6068,13 +6084,13 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG43" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>77</v>
@@ -6083,21 +6099,21 @@
         <v>97</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>260</v>
+        <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>261</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6105,7 +6121,7 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>76</v>
@@ -6120,15 +6136,17 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6153,13 +6171,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>77</v>
+        <v>262</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>77</v>
+        <v>264</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6177,7 +6195,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6192,21 +6210,21 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>77</v>
+        <v>265</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>266</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6214,10 +6232,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6226,16 +6244,16 @@
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>163</v>
+        <v>242</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>164</v>
+        <v>268</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>165</v>
+        <v>269</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6286,25 +6304,25 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>166</v>
+        <v>267</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -6312,21 +6330,21 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>169</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -6338,17 +6356,15 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -6397,19 +6413,19 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
@@ -6423,14 +6439,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>243</v>
+        <v>169</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6443,26 +6459,24 @@
         <v>77</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
         <v>130</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>244</v>
+        <v>170</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>245</v>
+        <v>171</v>
       </c>
       <c r="N47" t="s" s="2">
         <v>172</v>
       </c>
-      <c r="O47" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -6510,7 +6524,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>246</v>
+        <v>174</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -6528,7 +6542,7 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
@@ -6536,42 +6550,46 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>248</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I48" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J48" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -6619,36 +6637,36 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>272</v>
+        <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6656,7 +6674,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>85</v>
@@ -6671,7 +6689,7 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>275</v>
@@ -6704,13 +6722,13 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>278</v>
+        <v>77</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
@@ -6728,10 +6746,10 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH49" t="s" s="2">
         <v>85</v>
@@ -6743,13 +6761,13 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
     </row>
     <row r="50">
@@ -6780,13 +6798,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>282</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6813,13 +6831,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>283</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -6863,10 +6881,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6874,7 +6892,7 @@
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s" s="2">
         <v>85</v>
@@ -6889,13 +6907,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6946,10 +6964,10 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AG51" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AH51" t="s" s="2">
         <v>85</v>
@@ -6961,21 +6979,21 @@
         <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>288</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -6998,13 +7016,13 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>292</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7055,10 +7073,10 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>85</v>
@@ -7070,13 +7088,13 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>293</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="53">
@@ -7092,10 +7110,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7107,13 +7125,13 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>249</v>
+        <v>295</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7179,13 +7197,13 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54">
@@ -7201,10 +7219,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7213,16 +7231,16 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7279,7 +7297,7 @@
         <v>75</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -7288,13 +7306,13 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="55">
@@ -7313,7 +7331,7 @@
         <v>75</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7388,7 +7406,7 @@
         <v>75</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
@@ -7397,7 +7415,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7408,21 +7426,21 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -7491,13 +7509,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -7506,7 +7524,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -7524,14 +7542,14 @@
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>77</v>
+        <v>314</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
@@ -7543,17 +7561,15 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="N57" t="s" s="2">
         <v>317</v>
       </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -7617,12 +7633,123 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>77</v>
+        <v>298</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="O58" s="2"/>
+      <c r="P58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>77</v>
       </c>
     </row>

--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="324">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -415,6 +415,9 @@
   </si>
   <si>
     <t>EpisodeOfCare.extension</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t xml:space="preserve">Extension
@@ -2270,7 +2273,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>85</v>
+        <v>130</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>76</v>
@@ -2285,13 +2288,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2330,17 +2333,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -2352,7 +2355,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2366,13 +2369,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2394,13 +2397,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2451,7 +2454,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
@@ -2460,10 +2463,10 @@
         <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -2477,13 +2480,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>77</v>
@@ -2505,13 +2508,13 @@
         <v>77</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2562,7 +2565,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
@@ -2571,10 +2574,10 @@
         <v>76</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
@@ -2588,13 +2591,13 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
@@ -2616,13 +2619,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2673,7 +2676,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2682,10 +2685,10 @@
         <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
@@ -2699,13 +2702,13 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>77</v>
@@ -2727,13 +2730,13 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2784,7 +2787,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2793,10 +2796,10 @@
         <v>76</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
@@ -2810,13 +2813,13 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D14" t="s" s="2">
         <v>77</v>
@@ -2838,13 +2841,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2895,7 +2898,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2904,10 +2907,10 @@
         <v>76</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -2921,10 +2924,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2947,13 +2950,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3004,7 +3007,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -3030,14 +3033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3056,16 +3059,16 @@
         <v>77</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3103,19 +3106,19 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -3127,7 +3130,7 @@
         <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>77</v>
@@ -3141,13 +3144,13 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>77</v>
@@ -3169,13 +3172,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3226,7 +3229,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -3238,7 +3241,7 @@
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3252,10 +3255,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3278,13 +3281,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3335,7 +3338,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -3361,10 +3364,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3387,13 +3390,13 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3432,19 +3435,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -3456,7 +3459,7 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
@@ -3470,10 +3473,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3499,13 +3502,13 @@
         <v>99</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3513,7 +3516,7 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>77</v>
@@ -3555,7 +3558,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3581,10 +3584,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3607,13 +3610,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3640,11 +3643,11 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -3662,7 +3665,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3688,13 +3691,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -3716,13 +3719,13 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3773,7 +3776,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3785,7 +3788,7 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>77</v>
@@ -3799,10 +3802,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3825,13 +3828,13 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3882,7 +3885,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3908,10 +3911,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3934,13 +3937,13 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3979,19 +3982,19 @@
         <v>77</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -4003,7 +4006,7 @@
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>77</v>
@@ -4017,10 +4020,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4046,13 +4049,13 @@
         <v>99</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4060,7 +4063,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>77</v>
@@ -4102,7 +4105,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>85</v>
@@ -4128,10 +4131,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4154,13 +4157,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4211,7 +4214,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4237,13 +4240,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4265,13 +4268,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4322,7 +4325,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -4334,7 +4337,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4348,10 +4351,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4374,13 +4377,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4431,7 +4434,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -4457,10 +4460,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4483,13 +4486,13 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4528,19 +4531,19 @@
         <v>77</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>75</v>
@@ -4552,7 +4555,7 @@
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>77</v>
@@ -4566,10 +4569,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4595,13 +4598,13 @@
         <v>99</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4609,7 +4612,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>77</v>
@@ -4651,7 +4654,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>85</v>
@@ -4677,10 +4680,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4703,13 +4706,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4760,7 +4763,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4786,10 +4789,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4815,13 +4818,13 @@
         <v>99</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4829,7 +4832,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
@@ -4871,7 +4874,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>85</v>
@@ -4897,10 +4900,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4923,13 +4926,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4980,7 +4983,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5006,20 +5009,20 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>76</v>
@@ -5034,13 +5037,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5091,7 +5094,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -5100,10 +5103,10 @@
         <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -5117,14 +5120,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5143,19 +5146,19 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5204,7 +5207,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5216,7 +5219,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5230,10 +5233,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5256,13 +5259,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5313,7 +5316,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5328,21 +5331,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5368,13 +5371,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5400,13 +5403,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5424,7 +5427,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>85</v>
@@ -5439,21 +5442,21 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5476,13 +5479,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5533,7 +5536,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5559,10 +5562,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5585,13 +5588,13 @@
         <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5642,7 +5645,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>75</v>
@@ -5668,14 +5671,14 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -5694,16 +5697,16 @@
         <v>77</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5753,7 +5756,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5765,7 +5768,7 @@
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
@@ -5779,14 +5782,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5805,19 +5808,19 @@
         <v>86</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -5866,7 +5869,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5878,7 +5881,7 @@
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
@@ -5892,10 +5895,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5921,10 +5924,10 @@
         <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5951,13 +5954,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -5975,7 +5978,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>85</v>
@@ -6001,10 +6004,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6027,13 +6030,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6084,7 +6087,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -6110,10 +6113,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6136,16 +6139,16 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6171,13 +6174,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6195,7 +6198,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6210,21 +6213,21 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6247,13 +6250,13 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6304,7 +6307,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6330,10 +6333,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6356,13 +6359,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6413,7 +6416,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -6439,14 +6442,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6465,16 +6468,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6524,7 +6527,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>75</v>
@@ -6536,7 +6539,7 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -6550,14 +6553,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6576,19 +6579,19 @@
         <v>86</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6637,7 +6640,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6649,7 +6652,7 @@
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -6663,10 +6666,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6689,13 +6692,13 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6746,7 +6749,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>85</v>
@@ -6761,21 +6764,21 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6798,13 +6801,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6834,10 +6837,10 @@
         <v>109</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -6855,7 +6858,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -6881,10 +6884,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6907,13 +6910,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6964,7 +6967,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -6990,10 +6993,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7016,13 +7019,13 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7073,7 +7076,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7088,21 +7091,21 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7125,13 +7128,13 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7182,7 +7185,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7197,7 +7200,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
@@ -7208,10 +7211,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7234,13 +7237,13 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7291,7 +7294,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7306,21 +7309,21 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7343,13 +7346,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7400,7 +7403,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -7415,7 +7418,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7426,10 +7429,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7452,13 +7455,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7509,7 +7512,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7524,7 +7527,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -7535,14 +7538,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7561,13 +7564,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7618,7 +7621,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7633,7 +7636,7 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -7644,10 +7647,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7670,16 +7673,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7729,7 +7732,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>

--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2040" uniqueCount="326">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -570,6 +570,12 @@
   </si>
   <si>
     <t>function</t>
+  </si>
+  <si>
+    <t>The function of the participant</t>
+  </si>
+  <si>
+    <t>The code defining the function of the participant.</t>
   </si>
   <si>
     <t>EpisodeOfCare.extension:participant.extension:function.id</t>
@@ -3175,10 +3181,10 @@
         <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3255,10 +3261,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3364,10 +3370,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3473,10 +3479,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3502,13 +3508,13 @@
         <v>99</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3558,7 +3564,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -3584,10 +3590,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3610,13 +3616,13 @@
         <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3643,11 +3649,11 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -3665,7 +3671,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
@@ -3691,13 +3697,13 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>77</v>
@@ -3722,10 +3728,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3802,10 +3808,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3911,10 +3917,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4020,10 +4026,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4049,13 +4055,13 @@
         <v>99</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4063,7 +4069,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>77</v>
@@ -4105,7 +4111,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>85</v>
@@ -4131,10 +4137,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4157,13 +4163,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4214,7 +4220,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -4240,13 +4246,13 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>169</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>77</v>
@@ -4271,10 +4277,10 @@
         <v>131</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4351,10 +4357,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4460,10 +4466,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4569,10 +4575,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4598,13 +4604,13 @@
         <v>99</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4612,7 +4618,7 @@
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>77</v>
@@ -4654,7 +4660,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>85</v>
@@ -4680,10 +4686,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4709,10 +4715,10 @@
         <v>164</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4763,7 +4769,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4789,10 +4795,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4818,13 +4824,13 @@
         <v>99</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -4832,7 +4838,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
@@ -4874,7 +4880,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>85</v>
@@ -4900,10 +4906,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4926,13 +4932,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4983,7 +4989,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
@@ -5009,13 +5015,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>77</v>
@@ -5037,13 +5043,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5120,10 +5126,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5149,16 +5155,16 @@
         <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N35" t="s" s="2">
         <v>173</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5207,7 +5213,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -5233,10 +5239,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5259,13 +5265,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5316,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -5331,21 +5337,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5371,13 +5377,13 @@
         <v>105</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5403,13 +5409,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -5427,7 +5433,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>85</v>
@@ -5442,21 +5448,21 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5479,13 +5485,13 @@
         <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5536,7 +5542,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -5562,10 +5568,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5671,10 +5677,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5782,14 +5788,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -5811,16 +5817,16 @@
         <v>131</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>173</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -5869,7 +5875,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5895,10 +5901,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5924,10 +5930,10 @@
         <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5954,13 +5960,13 @@
         <v>77</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>77</v>
@@ -5978,7 +5984,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>85</v>
@@ -6004,10 +6010,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6030,13 +6036,13 @@
         <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6087,7 +6093,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -6113,10 +6119,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6139,16 +6145,16 @@
         <v>86</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6174,13 +6180,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6198,7 +6204,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -6213,21 +6219,21 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6250,13 +6256,13 @@
         <v>86</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6307,7 +6313,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -6333,10 +6339,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6442,10 +6448,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6553,14 +6559,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6582,16 +6588,16 @@
         <v>131</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>173</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6640,7 +6646,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -6666,10 +6672,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6692,13 +6698,13 @@
         <v>86</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6749,7 +6755,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>85</v>
@@ -6764,21 +6770,21 @@
         <v>97</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6801,13 +6807,13 @@
         <v>86</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6837,10 +6843,10 @@
         <v>109</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -6858,7 +6864,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>75</v>
@@ -6884,10 +6890,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -6910,13 +6916,13 @@
         <v>86</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6967,7 +6973,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>75</v>
@@ -6993,10 +6999,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7019,13 +7025,13 @@
         <v>86</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7076,7 +7082,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7091,21 +7097,21 @@
         <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7128,13 +7134,13 @@
         <v>86</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7185,7 +7191,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>75</v>
@@ -7200,7 +7206,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>77</v>
@@ -7211,10 +7217,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7237,13 +7243,13 @@
         <v>86</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7294,7 +7300,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>75</v>
@@ -7309,21 +7315,21 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7346,13 +7352,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7403,7 +7409,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>75</v>
@@ -7418,7 +7424,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>77</v>
@@ -7429,10 +7435,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7455,13 +7461,13 @@
         <v>77</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7512,7 +7518,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7527,7 +7533,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>77</v>
@@ -7538,14 +7544,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7564,13 +7570,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7621,7 +7627,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -7636,7 +7642,7 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>77</v>
@@ -7647,10 +7653,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7673,16 +7679,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7732,7 +7738,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>75</v>

--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
+++ b/fhir/StructureDefinition-ehealth-episodeofcare.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
